--- a/data/경상남도/창원시립도서관.xlsx
+++ b/data/경상남도/창원시립도서관.xlsx
@@ -16,14 +16,14 @@
     <sheet name="마산합포도서관" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="성주평생학습센터도서관" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="부림희망도서관" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="고향의봄도서관" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="진해아트홀도서관" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="진해아트홀도서관" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="고향의봄도서관" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="최윤덕도서관" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="상남도서관" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="남산평생학습센터도서관" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="동부도서관" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="남산평생학습센터도서관" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="동부도서관" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="반딧불이도서관" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="진해도서관" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="반딧불이도서관" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="상남도서관" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="용지호수어울림도서관" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="용지평생학습센터도서관" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="이미지도서관" sheetId="21" state="visible" r:id="rId21"/>
@@ -51,14 +51,14 @@
     <sheet name="성산도서관" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="천주평생학습센터도서관" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="마산회원도서관" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="의창평생학습센터도서관" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="합성가고파도서관" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="합성가고파도서관" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="의창평생학습센터도서관" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="양덕2동도서관" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="가음정평생학습센터도서관" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="회성동도서관" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="사림평생학습센터도서관" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="고운도서관" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="장천마을도서관" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="장천마을도서관" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="고운도서관" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="사파동성마을도서관" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="반림도서관" sheetId="55" state="visible" r:id="rId55"/>
     <sheet name="대방평생학습센터도서관" sheetId="56" state="visible" r:id="rId56"/>
@@ -575,6 +575,7 @@
           <t>843.6-이38파-v.v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음, 이미정 옮김</t>
@@ -597,6 +598,7 @@
           <t>843.6-이38파-v.v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음, 이미정 옮김</t>
@@ -614,6 +616,123 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코. 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843.6-이민진파-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[진해아트홀]종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코. 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843.6-이민진파-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[진해아트홀]종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>파친코. 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>843.6-이민진파-v.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[진해아트홀]종합자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -667,6 +786,7 @@
           <t>고향일반 843.6-이38파ㅊ-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 [지음] ; 신승미 옮김</t>
@@ -689,6 +809,7 @@
           <t>고향일반 843.6-이38파ㅊ-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -711,6 +832,7 @@
           <t>고향일반 863-뒤52파</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
@@ -719,120 +841,6 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>[고향]종합자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.6-이민진파-v.2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[진해아트홀]종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.6-이민진파-v.1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[진해아트홀]종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코. 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.6-이민진파-v.1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[진해아트홀]종합자료실</t>
         </is>
       </c>
     </row>
@@ -895,6 +903,7 @@
           <t>[최] 843.6-이38파2-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -917,6 +926,7 @@
           <t>[최] 843.6-이38파ㅊ-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 [지음] ; 신승미 옮김</t>
@@ -939,6 +949,7 @@
           <t>[최] 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -961,6 +972,7 @@
           <t>[최] 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -978,142 +990,6 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>상남일반 843-이38파ㅊ-v.2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[상남]종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>상남일반 843-이38파ㅊ-v.1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[상남]종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>상남일반 843.6-이38파-v.1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[상남]종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>상남일반 843.6-이38파-v.2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[상남]종합자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1167,6 +1043,7 @@
           <t>843-이38파-v.v1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -1189,6 +1066,7 @@
           <t>843-이38파-v.V2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -1205,7 +1083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1259,6 +1137,7 @@
           <t>843.6-이39파2-v.v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1281,6 +1160,7 @@
           <t>843.6-이39파2-v.v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1303,6 +1183,7 @@
           <t>다중 843.6-이39백</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>(美)李敏金 著 ; 刘勇军 译</t>
@@ -1325,6 +1206,7 @@
           <t>747.2-이39파</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>by Min Jin Lee</t>
@@ -1333,6 +1215,100 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>[동부]종합자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코/ 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843.6-이38파-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[반딧불이]일반자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코/ 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843.6-이38파-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 [지음]; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[반딧불이]일반자료실</t>
         </is>
       </c>
     </row>
@@ -1395,6 +1371,7 @@
           <t>843.6-이39파-v.v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1417,6 +1394,7 @@
           <t>843.6-이39파-v.v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1439,6 +1417,7 @@
           <t>843.6-이39파ㅊ-v.v.2</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1461,6 +1440,7 @@
           <t>843.6-이39파ㅊ-v.v.1</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1483,6 +1463,7 @@
           <t>747-이39파</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>by Minjin Lee</t>
@@ -1505,6 +1486,7 @@
           <t>다중 843.6-이39백</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>(美)李敏金 著 ; 刘勇军 译</t>
@@ -1527,14 +1509,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1567,44 +1549,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코/ 2</t>
+          <t>파친코. 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.6-이38파-v.2</t>
-        </is>
-      </c>
+          <t>상남일반 843-이38파ㅊ-v.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음; 신승미 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[반딧불이]일반자료실</t>
+          <t>[상남]종합자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코/ 1</t>
+          <t>파친코. 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.6-이38파-v.1</t>
-        </is>
-      </c>
+          <t>상남일반 843-이38파ㅊ-v.2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 [지음]; 신승미 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[반딧불이]일반자료실</t>
+          <t>[상남]종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>상남일반 843.6-이38파-v.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[상남]종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>상남일반 843.6-이38파-v.2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[상남]종합자료실</t>
         </is>
       </c>
     </row>
@@ -1667,6 +1697,7 @@
           <t>일반 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음</t>
@@ -1689,6 +1720,7 @@
           <t>일반 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음</t>
@@ -1759,6 +1791,7 @@
           <t>843-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음</t>
@@ -1781,6 +1814,7 @@
           <t>843.6-지67파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>지은이: 이민진</t>
@@ -1851,6 +1885,7 @@
           <t>일반 843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음; 이미정 옮김</t>
@@ -1873,6 +1908,7 @@
           <t>일반 843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 , 이미정 옮김</t>
@@ -1943,6 +1979,7 @@
           <t>성인 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음</t>
@@ -1965,6 +2002,7 @@
           <t>성인 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음</t>
@@ -2035,6 +2073,7 @@
           <t>일반 843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지은이</t>
@@ -2057,6 +2096,7 @@
           <t>일반 843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지은이</t>
@@ -2127,6 +2167,7 @@
           <t>843-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -2149,6 +2190,7 @@
           <t>843-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -2219,6 +2261,7 @@
           <t>성인 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음; 이미정 옮김</t>
@@ -2241,6 +2284,7 @@
           <t>성인 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음; 이미정 옮김</t>
@@ -2311,6 +2355,7 @@
           <t>843.6-이민진ㅍ-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -2333,6 +2378,7 @@
           <t>843.6-이민진ㅍ-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -2403,6 +2449,7 @@
           <t>843-이38파=c.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음; 신승미 옮김</t>
@@ -2425,6 +2472,7 @@
           <t>843-이38파=c.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -2447,6 +2495,7 @@
           <t>843-이38파=c.1</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 [지음] ; 신승미 옮김</t>
@@ -2469,6 +2518,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -2491,6 +2541,7 @@
           <t>843-이38파=c.2</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 지음; 신승미 옮김</t>
@@ -2513,6 +2564,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>이민진 지음 이미정 옮김</t>
@@ -2583,6 +2635,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -2605,6 +2658,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -2675,6 +2729,7 @@
           <t>843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -2697,6 +2752,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -2767,6 +2823,7 @@
           <t>일반 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 장편소설 ; 신승미 옮김</t>
@@ -2789,6 +2846,7 @@
           <t>일반 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 장편소설 신승미 옮김</t>
@@ -2859,6 +2917,7 @@
           <t>843-이38파1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -2881,6 +2940,7 @@
           <t>843.6-이67파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -2951,6 +3011,7 @@
           <t>일반 843-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -2973,6 +3034,7 @@
           <t>일반 843-이38파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -2995,6 +3057,7 @@
           <t>일반 843-이38파-v.1=c.2</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 (지은이), 신승미 (옮긴이)</t>
@@ -3017,6 +3080,7 @@
           <t>일반 843-이38파-v.2=c.2</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 (지은이), 신승미 (옮긴이)</t>
@@ -3087,6 +3151,7 @@
           <t>일반 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진지음;이미정옮김</t>
@@ -3109,6 +3174,7 @@
           <t>일반 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진지음;이미정옮김</t>
@@ -3179,6 +3245,7 @@
           <t>843.6-이민진ㅍ-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -3201,6 +3268,7 @@
           <t>843.6-이민진ㅍ-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -3271,6 +3339,7 @@
           <t>성인 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 글</t>
@@ -3293,6 +3362,7 @@
           <t>성인 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 글</t>
@@ -3363,6 +3433,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3385,6 +3456,7 @@
           <t>843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3455,6 +3527,7 @@
           <t>일반 843.6-이39파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -3477,6 +3550,7 @@
           <t>일반 843.6-이39파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -3547,6 +3621,7 @@
           <t>어른책 843-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3569,6 +3644,7 @@
           <t>어른책 843-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3639,6 +3715,7 @@
           <t>꿈산일반 843-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -3661,6 +3738,7 @@
           <t>꿈산일반 843-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -3683,6 +3761,7 @@
           <t>꿈산일반 843.6 v2-이38파</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -3705,6 +3784,7 @@
           <t>꿈산일반 843.6 v1-이38파</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -3775,6 +3855,7 @@
           <t>843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음; 이미정 옮김</t>
@@ -3797,6 +3878,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음; 이미정 옮김</t>
@@ -3867,6 +3949,7 @@
           <t>중앙일반 863-뒤52파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
@@ -3889,6 +3972,7 @@
           <t>중앙일반 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -3911,6 +3995,7 @@
           <t>중앙일반 843.6-이38파</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -3933,6 +4018,7 @@
           <t>중앙일반 843.6-이38파-v.4</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3955,6 +4041,7 @@
           <t>중앙일반 843.6-이38파-v.3</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 [지음] ; 신승미 옮김</t>
@@ -3977,6 +4064,7 @@
           <t>중앙영서 843.6-L479p</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>Min Jin Lee</t>
@@ -4047,6 +4135,7 @@
           <t>840-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음</t>
@@ -4069,6 +4158,7 @@
           <t>840-지67파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>지은이: 이민진</t>
@@ -4139,6 +4229,7 @@
           <t>일반 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음, 이미정 옮김</t>
@@ -4161,6 +4252,7 @@
           <t>일반 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음, 이미정 옮김</t>
@@ -4231,6 +4323,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -4253,6 +4346,7 @@
           <t>843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -4323,6 +4417,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4345,6 +4440,7 @@
           <t>843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4407,14 +4503,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>성산일반 843.6-이38파-v.1</t>
-        </is>
-      </c>
+          <t>성산일반 843.6-이38파-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4434,12 +4531,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>성산일반 843.6-이38파-v.2</t>
-        </is>
-      </c>
+          <t>성산일반 843.6-이38파2-v.2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4451,17 +4549,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>성산일반 843.6-이38파2-v.2</t>
-        </is>
-      </c>
+          <t>성산일반 843.6-이38파-v.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>이민진 지음 ; 이미정 옮김</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4481,6 +4580,7 @@
           <t>성산일반 843.6-이38파2-v.1</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 [지음] ; 신승미 옮김</t>
@@ -4551,6 +4651,7 @@
           <t>843-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4573,6 +4674,7 @@
           <t>843-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4643,6 +4745,7 @@
           <t>843.6-이민진ㅍ-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4665,6 +4768,7 @@
           <t>843.6-이민진ㅍ-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4682,6 +4786,100 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코 : PACHINKO. 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843-이38파-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이민정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[합성가고파]일반자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코 : PACHINKO. 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843-이38파-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이민정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[합성가고파]일반자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4735,6 +4933,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 (지은이) , 이미정 (옮긴이)</t>
@@ -4757,6 +4956,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 (지은이) , 신승미 (옮긴이)</t>
@@ -4765,98 +4965,6 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>[의창평생]일반자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : PACHINKO. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843-이38파-v.2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이민정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[합성가고파]일반자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : PACHINKO. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843-이38파-v.1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이민정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[합성가고파]일반자료실</t>
         </is>
       </c>
     </row>
@@ -4919,6 +5027,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -4941,6 +5050,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5011,6 +5121,7 @@
           <t>어른책 843-이38파-v.2=c.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5033,6 +5144,7 @@
           <t>어른책 843-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5055,6 +5167,7 @@
           <t>어른책 843-이38파-v.1=c.2</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5077,6 +5190,7 @@
           <t>어른책 843-이38파-v.1</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5147,6 +5261,7 @@
           <t>일반 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음; 신승미 옮김</t>
@@ -5169,6 +5284,7 @@
           <t>일반 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지은이, 옮긴이: 신승미</t>
@@ -5239,6 +5355,7 @@
           <t>843.6-이38파-v.2-2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5261,6 +5378,7 @@
           <t>843.6-이38파-v.2-1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5331,6 +5449,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 (지은이) , 신승미 (옮긴이)</t>
@@ -5353,6 +5472,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 (지은이) , 신승미 (옮긴이)</t>
@@ -5370,6 +5490,100 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코 2 - 개정판 : 이민진 장편소설</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843.6-이38파</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 (지은이) , 신승미 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[장천마을]일반자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코 1 - 개정판 : 이민진 장편소설</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843.6-이38파</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 (지은이) , 신승미 (옮긴이)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[장천마을]일반자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5423,6 +5637,7 @@
           <t>고운일반 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 (지은이), 신승미 (옮긴이)</t>
@@ -5445,6 +5660,7 @@
           <t>고운일반 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 (지은이), 신승미 (옮긴이)</t>
@@ -5453,98 +5669,6 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>[고운]일반자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 1 - 개정판 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.6-이38파</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 (지은이) , 신승미 (옮긴이)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[장천마을]일반자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 2 - 개정판 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.6-이38파</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 (지은이) , 신승미 (옮긴이)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[장천마을]일반자료실</t>
         </is>
       </c>
     </row>
@@ -5607,6 +5731,7 @@
           <t>813.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5629,6 +5754,7 @@
           <t>813.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5699,6 +5825,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 (지은이) , 신승미 (옮긴이)</t>
@@ -5721,6 +5848,7 @@
           <t>[최] 843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5791,6 +5919,7 @@
           <t>843-이319파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -5813,6 +5942,7 @@
           <t>843-이319파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -5883,6 +6013,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5905,6 +6036,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5975,6 +6107,7 @@
           <t>일반 843.6-이38파-2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -5997,6 +6130,7 @@
           <t>일반 843.6-이38파-1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6067,6 +6201,7 @@
           <t>843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6089,6 +6224,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6159,6 +6295,7 @@
           <t>명곡일반 843.6-이38파ㅇ</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김.</t>
@@ -6178,12 +6315,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>명곡일반 843.6-이38파ㅊ-v.1</t>
-        </is>
-      </c>
+          <t>명곡일반 843.6-이38파-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 [지음] ; 신승미 옮김</t>
+          <t>이민진 지음 ; 이미정 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6200,12 +6338,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>명곡일반 843.6-이38파-v.1</t>
-        </is>
-      </c>
+          <t>명곡일반 843.6-이38파ㅊ-v.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 [지음] ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6225,6 +6364,7 @@
           <t>명곡일반 843.6-이38파ㅊ-v.2</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -6247,6 +6387,7 @@
           <t>명곡일반 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -6269,6 +6410,7 @@
           <t>명곡일반 863-뒤52파</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
@@ -6339,6 +6481,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6361,6 +6504,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6431,6 +6575,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6453,6 +6598,7 @@
           <t>843.6-이99파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6523,6 +6669,7 @@
           <t>일반 843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6545,6 +6692,7 @@
           <t>일반 843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6615,6 +6763,7 @@
           <t>[여좌]일반자료 843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6637,6 +6786,7 @@
           <t>[여좌]일반자료 843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6707,6 +6857,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6729,6 +6880,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6799,6 +6951,7 @@
           <t>일반 843.6-이39파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6821,6 +6974,7 @@
           <t>일반 843.6-이39파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6891,6 +7045,7 @@
           <t>843-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6913,6 +7068,7 @@
           <t>843-이38파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -6983,6 +7139,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7005,6 +7162,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7075,6 +7233,7 @@
           <t>성인 843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7097,6 +7256,7 @@
           <t>성인 843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7167,6 +7327,7 @@
           <t>843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7189,6 +7350,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7259,6 +7421,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 , 이미정 옮김</t>
@@ -7281,6 +7444,7 @@
           <t>843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 , 이미정 옮김</t>
@@ -7351,6 +7515,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7373,6 +7538,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7443,6 +7609,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7465,6 +7632,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7535,6 +7703,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7557,6 +7726,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7627,6 +7797,7 @@
           <t>843.6-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7649,6 +7820,7 @@
           <t>843.6-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -7719,6 +7891,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음; 이미정 옮김</t>
@@ -7741,6 +7914,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -7811,6 +7985,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 (지은이), 신승미 (옮긴이)</t>
@@ -7833,6 +8008,7 @@
           <t>843.6-이38파</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 (지은이), 신승미 (옮긴이)</t>
@@ -7903,6 +8079,7 @@
           <t>일반 843.6-이민진파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -7925,6 +8102,7 @@
           <t>일반 843.6-이민진파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -7944,9 +8122,10 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>원서 843.6-리,파=c.2</t>
-        </is>
-      </c>
+          <t>원서 843.6-리,파</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>by Min Jin Lee</t>
@@ -7954,7 +8133,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[합포]보존서고(일반)</t>
+          <t>[합포]종합자료실</t>
         </is>
       </c>
     </row>
@@ -7966,9 +8145,10 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>원서 843.6-리,파</t>
-        </is>
-      </c>
+          <t>원서 843.6-리,파=c.2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>by Min Jin Lee</t>
@@ -7976,7 +8156,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[합포]종합자료실</t>
+          <t>[합포]보존서고(일반)</t>
         </is>
       </c>
     </row>
@@ -8039,6 +8219,7 @@
           <t>일반 843-이38파-v.1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진</t>
@@ -8061,6 +8242,7 @@
           <t>일반 843-이38파-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진</t>
